--- a/ksoft/_bakas/Papeis IP.xlsx
+++ b/ksoft/_bakas/Papeis IP.xlsx
@@ -1759,8 +1759,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F97EE73F6824CB4CBC81148F022C7122" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c135dfd5689eb1f41c942b6de29d974a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d196706a-de7c-4813-9c30-935ec1d4cc5d" xmlns:ns3="dd292427-de11-427f-a4cf-93902db2c621" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f598600a6f7a583361fdb2bebd14dd7" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F97EE73F6824CB4CBC81148F022C7122" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3acbdff660be4f41504a7377bd00bfbe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d196706a-de7c-4813-9c30-935ec1d4cc5d" xmlns:ns3="dd292427-de11-427f-a4cf-93902db2c621" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d165de6d9d878c1143ab435ba51092c" ns2:_="" ns3:_="">
     <xsd:import namespace="d196706a-de7c-4813-9c30-935ec1d4cc5d"/>
     <xsd:import namespace="dd292427-de11-427f-a4cf-93902db2c621"/>
     <xsd:element name="properties">
@@ -1850,7 +1850,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8e0251ee-03ea-4cdd-a84b-a8795fd5a69c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8e0251ee-03ea-4cdd-a84b-a8795fd5a69c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1876,7 +1876,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd292427-de11-427f-a4cf-93902db2c621" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1895,7 +1895,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -2034,13 +2034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9029082B-50D6-4BED-8DF1-B164324F5769}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D6A31F3-5140-46C8-A62A-1A6535140E5C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D203572-BA54-4452-B519-5775230EA09A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B20B06-CF33-4B25-8392-1A1DDDF539AF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7D697A9-192E-4E96-802F-2E7E4871778B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABC871E4-D46D-42B3-BE0B-4FB884FCA7A1}"/>
 </file>
--- a/ksoft/_bakas/Papeis IP.xlsx
+++ b/ksoft/_bakas/Papeis IP.xlsx
@@ -1759,8 +1759,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F97EE73F6824CB4CBC81148F022C7122" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3acbdff660be4f41504a7377bd00bfbe">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d196706a-de7c-4813-9c30-935ec1d4cc5d" xmlns:ns3="dd292427-de11-427f-a4cf-93902db2c621" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3d165de6d9d878c1143ab435ba51092c" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100F97EE73F6824CB4CBC81148F022C7122" ma:contentTypeVersion="19" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="c135dfd5689eb1f41c942b6de29d974a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d196706a-de7c-4813-9c30-935ec1d4cc5d" xmlns:ns3="dd292427-de11-427f-a4cf-93902db2c621" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f598600a6f7a583361fdb2bebd14dd7" ns2:_="" ns3:_="">
     <xsd:import namespace="d196706a-de7c-4813-9c30-935ec1d4cc5d"/>
     <xsd:import namespace="dd292427-de11-427f-a4cf-93902db2c621"/>
     <xsd:element name="properties">
@@ -1850,7 +1850,7 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8e0251ee-03ea-4cdd-a84b-a8795fd5a69c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de Imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="8e0251ee-03ea-4cdd-a84b-a8795fd5a69c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
@@ -1876,7 +1876,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd292427-de11-427f-a4cf-93902db2c621" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Partilhado Com" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1895,7 +1895,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Detalhes de Partilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -2034,13 +2034,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D6A31F3-5140-46C8-A62A-1A6535140E5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5662BD13-7B38-4B59-BFE5-B2ACA1EDDEC3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52B20B06-CF33-4B25-8392-1A1DDDF539AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C234A3-6A84-4C97-BC68-E8B0099B0DA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABC871E4-D46D-42B3-BE0B-4FB884FCA7A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF5D844C-3D74-48AD-8534-E14A6CE53A35}"/>
 </file>